--- a/apps/client/assets/templates/Sprache-word-import-template.xlsx
+++ b/apps/client/assets/templates/Sprache-word-import-template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단어 업로드" sheetId="1" r:id="Ra90618968f144cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 안내" sheetId="2" r:id="Rda7ddb22cda64ff6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="언어키 참고" sheetId="3" r:id="Ra78829a62a2c4ade"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단어 업로드" sheetId="1" r:id="R3e9bf230caaf4e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 안내" sheetId="2" r:id="R71c7d93127d145cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="언어키 참고" sheetId="3" r:id="R6b61216d24c34ad4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1652,26 +1652,28 @@
         <x:v>WHIP</x:v>
       </x:c>
       <x:c r="D11" s="19" t="str">
-        <x:v>이닝당 출루 허용률</x:v>
+        <x:v>투수가 한 이닝당 허용한 볼넷과 안타의 합</x:v>
       </x:c>
       <x:c r="E11" s="19" t="str">
-        <x:v>야구|투수 기록</x:v>
-      </x:c>
-      <x:c r="F11" s="19"/>
+        <x:v>투수 기록|기초 지표</x:v>
+      </x:c>
+      <x:c r="F11" s="19" t="str">
+        <x:v>other</x:v>
+      </x:c>
       <x:c r="G11" s="19" t="str">
-        <x:v>이닝당 출루 허용률|WHIP</x:v>
+        <x:v>이닝당 출루 허용률|이닝당 볼넷과 안타 허용 수</x:v>
       </x:c>
       <x:c r="H11" s="19"/>
       <x:c r="I11" s="19"/>
       <x:c r="J11" s="19"/>
       <x:c r="K11" s="19" t="str">
-        <x:v>이 투수의 WHIP는 1.10이다.</x:v>
+        <x:v>WHIP는 허용한 볼넷과 안타의 합을 투구 이닝으로 나누어 계산한다.</x:v>
       </x:c>
       <x:c r="L11" s="19" t="str">
-        <x:v>주자를 많이 내보내지 않았다.</x:v>
+        <x:v>허용 볼넷과 안타를 합한 뒤 투구 이닝으로 나눈 값이다.</x:v>
       </x:c>
       <x:c r="M11" s="19" t="str">
-        <x:v>이|투수의|WHIP는|1.10이다.</x:v>
+        <x:v>WHIP는|허용한|볼넷과|안타의|합을|투구|이닝으로|나누어|계산한다.</x:v>
       </x:c>
       <x:c r="N11" s="19"/>
       <x:c r="O11" s="19"/>
@@ -1687,25 +1689,31 @@
         <x:v>입문</x:v>
       </x:c>
       <x:c r="W11" s="19" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="X11" s="19" t="str">
-        <x:v>사용자 직접 정리</x:v>
+        <x:v>MLB Glossary</x:v>
       </x:c>
       <x:c r="Y11" s="19" t="str">
-        <x:v>private</x:v>
+        <x:v>reference-only; paraphrased fact</x:v>
       </x:c>
       <x:c r="Z11" s="26" t="str">
-        <x:v>1</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="AA11" s="26"/>
-      <x:c r="AB11" s="26"/>
+      <x:c r="AB11" s="26" t="str">
+        <x:v>https://www.mlb.com/glossary/standard-stats/walks-and-hits-per-inning-pitched</x:v>
+      </x:c>
       <x:c r="AC11" s="26"/>
-      <x:c r="AD11" s="26"/>
+      <x:c r="AD11" s="26" t="str">
+        <x:v>MLB Glossary의 공식 통계 설명을 한국어로 요약</x:v>
+      </x:c>
       <x:c r="AE11" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF11" s="26"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AF11" s="26" t="str">
+        <x:v>f64d5def-2065-5768-aeb0-8374e6a201ed</x:v>
+      </x:c>
       <x:c r="AG11" s="26" t="str">
         <x:v>general:baseball</x:v>
       </x:c>
@@ -1722,60 +1730,74 @@
         <x:v>ko</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>sentence</x:v>
+        <x:v>word</x:v>
       </x:c>
       <x:c r="C12" s="19" t="str">
-        <x:v>팬사인회는 응모 후 추첨으로 참여자를 정한다.</x:v>
+        <x:v>생얼</x:v>
       </x:c>
       <x:c r="D12" s="19" t="str">
-        <x:v>당첨된 팬이 행사에 참여한다.</x:v>
+        <x:v>화장하지 않은 자연스러운 얼굴</x:v>
       </x:c>
       <x:c r="E12" s="19" t="str">
-        <x:v>아이돌|팬 활동</x:v>
-      </x:c>
-      <x:c r="F12" s="19"/>
-      <x:c r="G12" s="19"/>
+        <x:v>팬덤 기초|표현</x:v>
+      </x:c>
+      <x:c r="F12" s="19" t="str">
+        <x:v>noun</x:v>
+      </x:c>
+      <x:c r="G12" s="19" t="str">
+        <x:v>민낯|화장하지 않은 얼굴|bare face</x:v>
+      </x:c>
       <x:c r="H12" s="19"/>
       <x:c r="I12" s="19"/>
       <x:c r="J12" s="19"/>
-      <x:c r="K12" s="19"/>
-      <x:c r="L12" s="19"/>
-      <x:c r="M12" s="19"/>
+      <x:c r="K12" s="19" t="str">
+        <x:v>자연스러운 생얼 사진이 공식 채널에 올라왔다.</x:v>
+      </x:c>
+      <x:c r="L12" s="19" t="str">
+        <x:v>화장하지 않은 자연스러운 얼굴 사진이 공식 채널에 올라왔다.</x:v>
+      </x:c>
+      <x:c r="M12" s="19" t="str">
+        <x:v>자연스러운|생얼|사진이|공식|채널에|올라왔다.</x:v>
+      </x:c>
       <x:c r="N12" s="19"/>
       <x:c r="O12" s="19"/>
       <x:c r="P12" s="19"/>
       <x:c r="Q12" s="19"/>
       <x:c r="R12" s="19"/>
       <x:c r="S12" s="19"/>
-      <x:c r="T12" s="19" t="str">
-        <x:v>팬사인회는|응모|후|추첨으로|참여자를|정한다.</x:v>
-      </x:c>
+      <x:c r="T12" s="19"/>
       <x:c r="U12" s="19" t="str">
-        <x:v>아이돌|일정</x:v>
+        <x:v>아이돌|표현</x:v>
       </x:c>
       <x:c r="V12" s="19" t="str">
-        <x:v>입문</x:v>
+        <x:v>초급</x:v>
       </x:c>
       <x:c r="W12" s="19" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X12" s="19" t="str">
-        <x:v>사용자 직접 정리</x:v>
+        <x:v>Korea.net K-pop Dictionary 소개</x:v>
       </x:c>
       <x:c r="Y12" s="19" t="str">
-        <x:v>private</x:v>
+        <x:v>reference-only; paraphrased fact</x:v>
       </x:c>
       <x:c r="Z12" s="26" t="str">
-        <x:v>1</x:v>
+        <x:v>2022-02-22</x:v>
       </x:c>
       <x:c r="AA12" s="26"/>
-      <x:c r="AB12" s="26"/>
+      <x:c r="AB12" s="26" t="str">
+        <x:v>https://www.korea.net/NewsFocus/Culture/view?articleId=211012</x:v>
+      </x:c>
       <x:c r="AC12" s="26"/>
-      <x:c r="AD12" s="26"/>
+      <x:c r="AD12" s="26" t="str">
+        <x:v>Korea.net의 K-pop dictionary 소개 내용을 한국어로 요약</x:v>
+      </x:c>
       <x:c r="AE12" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF12" s="26"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AF12" s="26" t="str">
+        <x:v>14eccebd-807a-5497-b745-89c8c89a2740</x:v>
+      </x:c>
       <x:c r="AG12" s="26" t="str">
         <x:v>general:idol-fandom</x:v>
       </x:c>
@@ -8975,7 +8997,7 @@
         <x:v>선택</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>비우면 표현·뜻·품사로 안정적인 ID를 자동 생성</x:v>
+        <x:v>비우면 표현·뜻·품사로 ID를 자동 생성. 공유·번들 항목은 최초 배포 ID를 고정해 이후 문구 교정에도 유지</x:v>
       </x:c>
       <x:c r="D36" s="26" t="str">
         <x:v>직접 정한 고유 ID</x:v>
